--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487866_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487866_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2724</v>
+        <v>6.6764</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2001</v>
+        <v>3.9858</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0722</v>
+        <v>2.6906</v>
       </c>
       <c r="G2" t="n">
         <v>3.7328</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8299</v>
+        <v>0.2339</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0562</v>
+        <v>-0.2705</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8861</v>
+        <v>0.5044</v>
       </c>
       <c r="V2" t="n">
         <v>3.7503</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.824</v>
+        <v>6.6375</v>
       </c>
       <c r="E3" t="n">
-        <v>2.905</v>
+        <v>3.0121</v>
       </c>
       <c r="F3" t="n">
-        <v>3.919</v>
+        <v>3.6254</v>
       </c>
       <c r="G3" t="n">
         <v>6.0725</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0033</v>
+        <v>-0.1831</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9786</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9819</v>
+        <v>0.6884</v>
       </c>
       <c r="V3" t="n">
         <v>0.1238</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4051</v>
+        <v>4.3273</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5032</v>
+        <v>0.396</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9019</v>
+        <v>3.9313</v>
       </c>
       <c r="G4" t="n">
         <v>1.6651</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3863</v>
+        <v>0.3085</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0562</v>
+        <v>-0.1633</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4424</v>
+        <v>0.4718</v>
       </c>
       <c r="V4" t="n">
         <v>1.5213</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0904</v>
+        <v>3.7366</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3149</v>
+        <v>1.6364</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7754</v>
+        <v>2.1002</v>
       </c>
       <c r="G5" t="n">
         <v>4.273</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.858</v>
+        <v>0.5042</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4443</v>
+        <v>-0.1228</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3023</v>
+        <v>0.627</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8211</v>
+        <v>3.2765</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8577</v>
+        <v>2.1076</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9634</v>
+        <v>1.1689</v>
       </c>
       <c r="G6" t="n">
         <v>3.7864</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.214</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.332</v>
+        <v>-0.4181</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.546</v>
+        <v>-0.3405</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5838</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1682</v>
+        <v>1.569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6484</v>
+        <v>0.7556</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5198</v>
+        <v>0.8134</v>
       </c>
       <c r="G7" t="n">
         <v>2.1865</v>
@@ -1000,13 +1000,13 @@
         <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1182</v>
+        <v>-0.7175</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4658</v>
+        <v>-0.1722</v>
       </c>
       <c r="V7" t="n">
         <v>-1.9813</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6078</v>
+        <v>1.5356</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5405</v>
+        <v>-0.1119</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1483</v>
+        <v>1.6474</v>
       </c>
       <c r="G8" t="n">
         <v>2.4744</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.2828</v>
+        <v>-1.355</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9663</v>
+        <v>-0.5376</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3165</v>
+        <v>-0.8174</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.877</v>
+        <v>-0.6422</v>
       </c>
       <c r="E9" t="n">
         <v>-2.2984</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4214</v>
+        <v>1.6562</v>
       </c>
       <c r="G9" t="n">
         <v>0.4232</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3002</v>
+        <v>-1.0654</v>
       </c>
       <c r="T9" t="n">
         <v>-0.5872000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7131</v>
+        <v>-0.4782</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4634</v>
+        <v>-1.2682</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9255</v>
+        <v>-1.8184</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4621</v>
+        <v>0.5502</v>
       </c>
       <c r="G10" t="n">
         <v>2.186</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0438</v>
+        <v>-0.8486</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8482</v>
+        <v>-0.741</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1957</v>
+        <v>-0.1076</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9813</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>25.8486</v>
+        <v>25.8485</v>
       </c>
       <c r="E11" t="n">
-        <v>7.664899999999999</v>
+        <v>7.6648</v>
       </c>
       <c r="F11" t="n">
-        <v>18.1835</v>
+        <v>18.1836</v>
       </c>
       <c r="G11" t="n">
         <v>26.7999</v>
@@ -1312,13 +1312,13 @@
         <v>14.5683</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.881500000000001</v>
+        <v>-3.881600000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.257400000000001</v>
+        <v>-4.2573</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3755999999999999</v>
+        <v>0.3756999999999998</v>
       </c>
       <c r="V11" t="n">
         <v>0.8490000000000002</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CHACON CARNERO</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6563</v>
+        <v>2.1898</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5316</v>
+        <v>1.5084</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1247</v>
+        <v>0.6814</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8248</v>
+        <v>-2.9857</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9677</v>
+        <v>-1.3561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1429</v>
+        <v>-1.6296</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5432</v>
+        <v>-1.52</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2576</v>
+        <v>-0.67</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7144</v>
+        <v>-0.8499</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2816</v>
+        <v>-1.4658</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2899</v>
+        <v>-0.6861</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5715</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4766</v>
+        <v>0.7648</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6742</v>
+        <v>-0.0423</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8025</v>
+        <v>0.8071</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6452</v>
+        <v>5.2432</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4776</v>
+        <v>5.36</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>J. CHACON CARNERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2469</v>
+        <v>0.999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9727</v>
+        <v>1.1386</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2743</v>
+        <v>-0.1396</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9857</v>
+        <v>0.8248</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3561</v>
+        <v>0.9677</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6296</v>
+        <v>-0.1429</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.52</v>
+        <v>0.5432</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.67</v>
+        <v>1.2576</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8499</v>
+        <v>-0.7144</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4658</v>
+        <v>0.2816</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6861</v>
+        <v>-0.2899</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0.5715</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1781</v>
+        <v>1.8194</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5780999999999999</v>
+        <v>1.2811</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4</v>
+        <v>0.5383</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2432</v>
+        <v>-1.6452</v>
       </c>
       <c r="W13" t="n">
-        <v>5.36</v>
+        <v>-0.4776</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1168</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6217</v>
+        <v>0.099</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5868</v>
+        <v>1.3369</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2085</v>
+        <v>-1.2379</v>
       </c>
       <c r="G14" t="n">
         <v>0.8265</v>
@@ -1546,13 +1546,13 @@
         <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.032</v>
+        <v>0.6888</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3791</v>
+        <v>0.371</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3471</v>
+        <v>0.3178</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5838</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9529</v>
+        <v>0.0321</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5409</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.588</v>
+        <v>0.8229</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6138</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1533</v>
+        <v>1.1383</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5129</v>
+        <v>0.2372</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6661</v>
+        <v>0.901</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1168</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3311</v>
+        <v>-1.3105</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0192</v>
+        <v>-0.2335</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3119</v>
+        <v>-1.0771</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2653</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1977</v>
+        <v>-0.1771</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2829</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1292</v>
+        <v>0.1057</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1168</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9329</v>
+        <v>-3.1306</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7143</v>
+        <v>-3.1429</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2186</v>
+        <v>0.0123</v>
       </c>
       <c r="G17" t="n">
         <v>-3.2359</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2511</v>
+        <v>0.0535</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2544</v>
+        <v>-0.1743</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0032</v>
+        <v>0.2277</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3644</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4361</v>
+        <v>-3.3393</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9159</v>
+        <v>-3.7016</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4798</v>
+        <v>0.3624</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0192</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4169</v>
+        <v>-0.32</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-0.6338</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4313</v>
+        <v>0.3138</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1545</v>
+        <v>-4.2519</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0305</v>
+        <v>-3.1027</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1239</v>
+        <v>-1.1492</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4289</v>
+        <v>-4.6509</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.439</v>
+        <v>-2.0555</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.9899</v>
+        <v>-2.5954</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.763</v>
+        <v>-2.6832</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0554</v>
+        <v>-1.3328</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.8183</v>
+        <v>-1.3504</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6659</v>
+        <v>-1.9677</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4943</v>
+        <v>-0.7227</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1716</v>
+        <v>-1.245</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0257</v>
+        <v>-0.4117</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9811</v>
+        <v>-0.4195</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0446</v>
+        <v>0.0078</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8567</v>
+        <v>-4.7235</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5313</v>
+        <v>-2.5663</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3254</v>
+        <v>-2.1572</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.6509</v>
+        <v>-4.4289</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0555</v>
+        <v>-0.439</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5954</v>
+        <v>-3.9899</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6832</v>
+        <v>-1.763</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3328</v>
+        <v>1.0554</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3504</v>
+        <v>-2.8183</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9677</v>
+        <v>-2.6659</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7227</v>
+        <v>-1.4943</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.245</v>
+        <v>-1.1716</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0165</v>
+        <v>1.4566</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8482</v>
+        <v>0.4454</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1683</v>
+        <v>1.0113</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5586</v>
+        <v>-5.8436</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5676</v>
+        <v>-3.7407</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9911</v>
+        <v>-2.1029</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2838</v>
+        <v>-2.9676</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5457</v>
+        <v>1.5522</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7382</v>
+        <v>-4.5197</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.312</v>
+        <v>0.4372</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.676</v>
+        <v>2.7159</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.636</v>
+        <v>-2.2787</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9719</v>
+        <v>-3.4048</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8697</v>
+        <v>-1.1637</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1022</v>
+        <v>-2.2411</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4974</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1311</v>
+        <v>0.0107</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1338</v>
+        <v>-0.7024</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0026</v>
+        <v>0.7131</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3538</v>
+        <v>-1.6381</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3538</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9072</v>
+        <v>-5.8546</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.955</v>
+        <v>-4.889</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9522</v>
+        <v>-0.9656</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9676</v>
+        <v>-3.2838</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5522</v>
+        <v>-1.5457</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.5197</v>
+        <v>-1.7382</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4372</v>
+        <v>-1.312</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7159</v>
+        <v>-0.676</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2787</v>
+        <v>-0.636</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4048</v>
+        <v>-1.9719</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1637</v>
+        <v>-0.8697</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2411</v>
+        <v>-1.1022</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.2487</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0529</v>
+        <v>-0.4272</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9167</v>
+        <v>-0.4553</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8639</v>
+        <v>0.0281</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6381</v>
+        <v>0.3538</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2843</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-25.8485</v>
+        <v>-25.1341</v>
       </c>
       <c r="E23" t="n">
         <v>-18.1836</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.6648</v>
+        <v>-6.9505</v>
       </c>
       <c r="G23" t="n">
         <v>-26.7998</v>
@@ -2221,13 +2221,13 @@
         <v>-15.3285</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.918199999999999</v>
+        <v>-8.918200000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.713199999999999</v>
+        <v>-3.7132</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.2049</v>
+        <v>-5.204900000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-17.8819</v>
@@ -2248,22 +2248,22 @@
         <v>12.4871</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8815</v>
+        <v>4.596100000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3758</v>
+        <v>-0.3758000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>4.2574</v>
+        <v>4.971700000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8494</v>
+        <v>-0.8494000000000005</v>
       </c>
       <c r="W23" t="n">
         <v>5.678400000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.527700000000001</v>
+        <v>-6.5277</v>
       </c>
     </row>
   </sheetData>
